--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487685_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487685_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7004</v>
+        <v>4.6012</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8597</v>
+        <v>6.7606</v>
       </c>
       <c r="F2" t="n">
         <v>-2.1593</v>
@@ -610,10 +610,10 @@
         <v>2.5224</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0718</v>
+        <v>0.9727</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6057</v>
+        <v>0.2952</v>
       </c>
       <c r="U2" t="n">
         <v>0.6775</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>A. ARMSTRONG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5652</v>
+        <v>3.4014</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6888</v>
+        <v>2.9892</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1236</v>
+        <v>0.4122</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0598</v>
+        <v>4.1005</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9089</v>
+        <v>1.5439</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8491</v>
+        <v>2.5565</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9273</v>
+        <v>6.7501</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9124</v>
+        <v>2.414</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0149</v>
+        <v>4.3361</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.8675</v>
+        <v>-2.6496</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0035</v>
+        <v>-0.87</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.8641</v>
+        <v>-1.7796</v>
       </c>
       <c r="P3" t="n">
         <v>-1.5523</v>
@@ -688,22 +688,22 @@
         <v>2.5224</v>
       </c>
       <c r="S3" t="n">
-        <v>5.4039</v>
+        <v>0.9278</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8839</v>
+        <v>0.3137</v>
       </c>
       <c r="U3" t="n">
-        <v>1.52</v>
+        <v>0.6141</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.3463</v>
+        <v>-0.0746</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2985</v>
+        <v>-0.0746</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4441</v>
+        <v>2.0709</v>
       </c>
       <c r="E4" t="n">
-        <v>6.055</v>
+        <v>5.6546</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.6109</v>
+        <v>-3.5837</v>
       </c>
       <c r="G4" t="n">
         <v>-2.0111</v>
@@ -766,13 +766,13 @@
         <v>2.7164</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6074</v>
+        <v>1.2343</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2146</v>
+        <v>0.8142</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3928</v>
+        <v>0.4201</v>
       </c>
       <c r="V4" t="n">
         <v>1.1015</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ARMSTRONG</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.055</v>
+        <v>0.4994</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8881</v>
+        <v>0.3714</v>
       </c>
       <c r="F5" t="n">
-        <v>0.167</v>
+        <v>0.128</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1005</v>
+        <v>-1.1726</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5439</v>
+        <v>-1.202</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5565</v>
+        <v>0.0295</v>
       </c>
       <c r="J5" t="n">
-        <v>6.7501</v>
+        <v>0.0859</v>
       </c>
       <c r="K5" t="n">
-        <v>2.414</v>
+        <v>0.0453</v>
       </c>
       <c r="L5" t="n">
-        <v>4.3361</v>
+        <v>0.0406</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6496</v>
+        <v>-1.2585</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.87</v>
+        <v>-1.2473</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7796</v>
+        <v>-0.0111</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5523</v>
+        <v>0.9702</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.0747</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5224</v>
+        <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4186</v>
+        <v>0.0421</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7874</v>
+        <v>0.2854</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3688</v>
+        <v>-0.2434</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0746</v>
+        <v>0.6597</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.0746</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8086</v>
+        <v>0.0176</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5716</v>
+        <v>1.3865</v>
       </c>
       <c r="F6" t="n">
-        <v>0.237</v>
+        <v>-1.3689</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1726</v>
+        <v>0.0598</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.202</v>
+        <v>1.9089</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0295</v>
+        <v>-1.8491</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0859</v>
+        <v>3.9273</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0453</v>
+        <v>2.9124</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0406</v>
+        <v>1.0149</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2585</v>
+        <v>-3.8675</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2473</v>
+        <v>-1.0035</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0111</v>
+        <v>-2.8641</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9702</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.0747</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9702</v>
+        <v>2.5224</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3513</v>
+        <v>2.8564</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4856</v>
+        <v>1.5817</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1343</v>
+        <v>1.2747</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6597</v>
+        <v>-1.3463</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6597</v>
+        <v>-1.2985</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9204</v>
+        <v>-0.5111</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0792</v>
+        <v>-0.7789</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1588</v>
+        <v>0.2678</v>
       </c>
       <c r="G7" t="n">
         <v>0.1129</v>
@@ -1000,13 +1000,13 @@
         <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3154</v>
+        <v>0.0939</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1211</v>
+        <v>0.1792</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1943</v>
+        <v>-0.0852</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3299</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BUSTOS NGUEMA</t>
+          <t>E. CALVO SALVE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1631</v>
+        <v>-2.0151</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7715</v>
+        <v>-1.2674</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3917</v>
+        <v>-0.7477</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3641</v>
+        <v>-1.5042</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3009</v>
+        <v>-0.8552</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.665</v>
+        <v>-0.649</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3183</v>
+        <v>0.4937</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6025</v>
+        <v>0.4531</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9208</v>
+        <v>0.0406</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0458</v>
+        <v>-1.9979</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3015</v>
+        <v>-1.3083</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2558</v>
+        <v>-0.6896</v>
       </c>
       <c r="P8" t="n">
+        <v>-1.1642</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.9403</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-3.1045</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9771</v>
+        <v>-0.0064</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6992</v>
+        <v>0.1792</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2779</v>
+        <v>-0.1856</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8358</v>
+        <v>0.6597</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.788</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. CALVO SALVE</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3427</v>
+        <v>-2.1378</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5677</v>
+        <v>-1.3134</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7749</v>
+        <v>-0.8244</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5042</v>
+        <v>-4.2756</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8552</v>
+        <v>-0.257</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.649</v>
+        <v>-4.0185</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4937</v>
+        <v>0.4649</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4531</v>
+        <v>0.8074</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0406</v>
+        <v>-0.3426</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9979</v>
+        <v>-4.7404</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3083</v>
+        <v>-1.0645</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6896</v>
+        <v>-3.676</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9403</v>
+        <v>-2.1344</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7761</v>
+        <v>2.3284</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.334</v>
+        <v>1.1244</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1211</v>
+        <v>0.074</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2129</v>
+        <v>1.0504</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6597</v>
+        <v>0.8194</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6597</v>
+        <v>0.5373</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>J. BUSTOS NGUEMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6388</v>
+        <v>-2.7548</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1142</v>
+        <v>-2.4722</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5246</v>
+        <v>-0.2826</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.2756</v>
+        <v>-0.3641</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.257</v>
+        <v>1.3009</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.0185</v>
+        <v>-1.665</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4649</v>
+        <v>-0.3183</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8074</v>
+        <v>1.6025</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3426</v>
+        <v>-1.9208</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.7404</v>
+        <v>-0.0458</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0645</v>
+        <v>-0.3015</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.676</v>
+        <v>0.2558</v>
       </c>
       <c r="P10" t="n">
-        <v>0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1344</v>
+        <v>-3.1045</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3284</v>
+        <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6234</v>
+        <v>1.3854</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7268</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3502</v>
+        <v>0.387</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8194</v>
+        <v>-1.8358</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2821</v>
+        <v>-0.0478</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5373</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7045</v>
+        <v>-4.3681</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2768</v>
+        <v>-3.0766</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4277</v>
+        <v>-1.2914</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9105</v>
@@ -1312,13 +1312,13 @@
         <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3701</v>
+        <v>0.7066</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2434</v>
+        <v>0.4436</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1267</v>
+        <v>0.263</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6119</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.196199999999998</v>
+        <v>-1.196399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>8.253799999999998</v>
+        <v>8.253800000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.4499</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.972199999999999</v>
+        <v>-2.9722</v>
       </c>
       <c r="H12" t="n">
         <v>0.4201999999999999</v>
@@ -1390,19 +1390,19 @@
         <v>17.4628</v>
       </c>
       <c r="S12" t="n">
-        <v>9.337</v>
+        <v>9.337199999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>5.1646</v>
+        <v>5.1647</v>
       </c>
       <c r="U12" t="n">
-        <v>4.1724</v>
+        <v>4.1726</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7403</v>
       </c>
       <c r="W12" t="n">
-        <v>3.7147</v>
+        <v>3.714700000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-5.455000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5092</v>
+        <v>6.0369</v>
       </c>
       <c r="E13" t="n">
-        <v>7.0648</v>
+        <v>7.1649</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5556</v>
+        <v>-1.128</v>
       </c>
       <c r="G13" t="n">
         <v>4.8291</v>
@@ -1468,13 +1468,13 @@
         <v>3.4926</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-1.0131</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.544</v>
+        <v>-0.4439</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0032</v>
+        <v>-0.5692</v>
       </c>
       <c r="V13" t="n">
         <v>1.6388</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6798</v>
+        <v>1.2249</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7262</v>
+        <v>2.3258</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0464</v>
+        <v>-1.1009</v>
       </c>
       <c r="G14" t="n">
         <v>1.6457</v>
@@ -1546,13 +1546,13 @@
         <v>3.4926</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2734</v>
+        <v>-1.7283</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.544</v>
+        <v>-0.9444</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7294</v>
+        <v>-0.7839</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2448</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1971</v>
+        <v>0.8539</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3827</v>
+        <v>-0.3235</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1856</v>
+        <v>1.1774</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9613</v>
+        <v>-0.6989</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0191</v>
+        <v>-1.656</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0578</v>
+        <v>0.9571</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7413</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6601</v>
+        <v>-1.2935</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.6901</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.78</v>
+        <v>-0.0956</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.641</v>
+        <v>-0.3625</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.139</v>
+        <v>0.2669</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6254</v>
+        <v>-0.5636</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9713000000000001</v>
+        <v>-0.2843</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3459</v>
+        <v>-0.2793</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.5537</v>
+        <v>0.5642</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3299</v>
+        <v>0.5642</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0105</v>
+        <v>0.8465</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2465</v>
+        <v>1.9462</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.236</v>
+        <v>-1.0997</v>
       </c>
       <c r="G16" t="n">
         <v>2.1908</v>
@@ -1702,13 +1702,13 @@
         <v>2.5224</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1698</v>
+        <v>-1.3338</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3623</v>
+        <v>-0.6626</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8075</v>
+        <v>-0.6712</v>
       </c>
       <c r="V16" t="n">
         <v>0.3776</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7627</v>
+        <v>0.7784</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5237000000000001</v>
+        <v>1.8822</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2864</v>
+        <v>-1.1038</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6989</v>
+        <v>0.9613</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.656</v>
+        <v>1.0191</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9571</v>
+        <v>-0.0578</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6032999999999999</v>
+        <v>1.7413</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2935</v>
+        <v>1.6601</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6901</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0956</v>
+        <v>-0.78</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3625</v>
+        <v>-0.641</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2669</v>
+        <v>-0.139</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6548</v>
+        <v>0.2066</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4845</v>
+        <v>0.4708</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1702</v>
+        <v>-0.2641</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5642</v>
+        <v>-1.5537</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5642</v>
+        <v>-0.3299</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0172</v>
+        <v>0.0717</v>
       </c>
       <c r="E18" t="n">
         <v>-0.2017</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2188</v>
+        <v>0.2733</v>
       </c>
       <c r="G18" t="n">
         <v>0.1625</v>
@@ -1858,13 +1858,13 @@
         <v>0.194</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3394</v>
+        <v>-0.2849</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2423</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0426</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6731</v>
+        <v>-0.3456</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9105</v>
+        <v>-0.6102</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2374</v>
+        <v>0.2646</v>
       </c>
       <c r="G19" t="n">
         <v>0.206</v>
@@ -1936,13 +1936,13 @@
         <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6851</v>
+        <v>-0.3575</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3028</v>
+        <v>-0.0025</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3822</v>
+        <v>-0.355</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9767</v>
+        <v>-1.113</v>
       </c>
       <c r="E20" t="n">
         <v>0.372</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3487</v>
+        <v>-1.485</v>
       </c>
       <c r="G20" t="n">
         <v>0.0521</v>
@@ -2014,13 +2014,13 @@
         <v>3.2985</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0004</v>
+        <v>-1.1367</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4834</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.517</v>
+        <v>-0.6533</v>
       </c>
       <c r="V20" t="n">
         <v>0.5537</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3659</v>
+        <v>-2.7202</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7722</v>
+        <v>-0.3719</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5936</v>
+        <v>-2.3483</v>
       </c>
       <c r="G21" t="n">
         <v>-4.5407</v>
@@ -2092,13 +2092,13 @@
         <v>3.2985</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.1043</v>
+        <v>-1.4586</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9691</v>
+        <v>-0.5687</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1352</v>
+        <v>-0.8899</v>
       </c>
       <c r="V21" t="n">
         <v>1.9209</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9646</v>
+        <v>-4.4373</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9342</v>
+        <v>-2.734</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0304</v>
+        <v>-1.7033</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8358</v>
@@ -2170,13 +2170,13 @@
         <v>3.4926</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1945</v>
+        <v>-1.6672</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2113</v>
+        <v>-1.0111</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9832</v>
+        <v>-0.6561</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5164</v>
@@ -2206,7 +2206,7 @@
         <v>1.1962</v>
       </c>
       <c r="E23" t="n">
-        <v>9.449900000000001</v>
+        <v>9.4498</v>
       </c>
       <c r="F23" t="n">
         <v>-8.2537</v>
@@ -2215,7 +2215,7 @@
         <v>2.972099999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4202999999999988</v>
+        <v>-0.4202999999999997</v>
       </c>
       <c r="I23" t="n">
         <v>3.3924</v>
@@ -2254,7 +2254,7 @@
         <v>-4.1724</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.1645</v>
+        <v>-5.1646</v>
       </c>
       <c r="V23" t="n">
         <v>1.7403</v>
